--- a/data/memories/memory_01/locales/es/documents/director/Employee_Registry_Previous.xlsx
+++ b/data/memories/memory_01/locales/es/documents/director/Employee_Registry_Previous.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee Registry Previous</t>
+          <t>Registro de Empleados Anterior</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,38 +469,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Previous Employee Registry</t>
+          <t>Registro de Empleados Anteriores</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Archived version retained for comparison with the current registry.</t>
+          <t>Se conserva la versión archivada para compararla con el registro actual.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Posición</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HORA</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
     </row>
@@ -580,19 +580,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Administración</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Keep this version available when investigating historical organisational changes.</t>
+          <t>Mantenga esta versión disponible cuando investigue cambios organizacionales históricos.</t>
         </is>
       </c>
     </row>
